--- a/src/test/resources/Credentialss.xlsx
+++ b/src/test/resources/Credentialss.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Flightbookingdetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="141">
   <si>
     <t xml:space="preserve">Flight booking – Corporate Admin</t>
   </si>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Booked by Corporate admin</t>
   </si>
   <si>
-    <t xml:space="preserve">Mum</t>
+    <t xml:space="preserve">Chennai</t>
   </si>
   <si>
     <t xml:space="preserve">New client</t>
@@ -182,9 +182,6 @@
     <t xml:space="preserve">Pickup location</t>
   </si>
   <si>
-    <t xml:space="preserve">Chennai</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nothing</t>
   </si>
   <si>
@@ -212,13 +209,37 @@
     <t xml:space="preserve">Onward date</t>
   </si>
   <si>
+    <t xml:space="preserve">Indi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tourist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultipleEntry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No of Pax</t>
+  </si>
+  <si>
     <t xml:space="preserve">India</t>
   </si>
   <si>
-    <t xml:space="preserve">Tourist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MultipleEntry</t>
+    <t xml:space="preserve">Silver</t>
   </si>
   <si>
     <t xml:space="preserve">Passenger information</t>
@@ -248,24 +269,36 @@
     <t xml:space="preserve">Employee name</t>
   </si>
   <si>
+    <t xml:space="preserve">Nominee name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sundara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pandiyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selvacorporate8@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation-user one-1111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Guest</t>
   </si>
   <si>
-    <t xml:space="preserve">Mr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sundara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pandiyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s1@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation-user one-1111</t>
-  </si>
-  <si>
     <t xml:space="preserve">Karhi</t>
   </si>
   <si>
@@ -278,6 +311,9 @@
     <t xml:space="preserve">Automation-user two-2222</t>
   </si>
   <si>
+    <t xml:space="preserve">Sanjay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Harish</t>
   </si>
   <si>
@@ -290,6 +326,9 @@
     <t xml:space="preserve">Automation-user three-3333</t>
   </si>
   <si>
+    <t xml:space="preserve">Sujay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Poovarasan</t>
   </si>
   <si>
@@ -302,6 +341,9 @@
     <t xml:space="preserve">Automation-four-4444</t>
   </si>
   <si>
+    <t xml:space="preserve">Kajay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ilaku</t>
   </si>
   <si>
@@ -314,6 +356,9 @@
     <t xml:space="preserve">Automation-five-5555</t>
   </si>
   <si>
+    <t xml:space="preserve">Majay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dhileep</t>
   </si>
   <si>
@@ -326,6 +371,9 @@
     <t xml:space="preserve">Automation-six-6666</t>
   </si>
   <si>
+    <t xml:space="preserve">Tajay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Syed</t>
   </si>
   <si>
@@ -338,6 +386,9 @@
     <t xml:space="preserve">Automation-eight-7777</t>
   </si>
   <si>
+    <t xml:space="preserve">Zajay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sew</t>
   </si>
   <si>
@@ -350,6 +401,9 @@
     <t xml:space="preserve">Automation-eight-8888</t>
   </si>
   <si>
+    <t xml:space="preserve">Yajay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reee</t>
   </si>
   <si>
@@ -357,6 +411,9 @@
   </si>
   <si>
     <t xml:space="preserve">Automation-seven-9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lajay</t>
   </si>
   <si>
     <t xml:space="preserve">International Passenger details</t>
@@ -642,8 +699,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.48"/>
@@ -730,7 +787,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -1268,19 +1325,19 @@
         <v>43</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>30</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>45</v>
@@ -1294,19 +1351,19 @@
         <v>46</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>30</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>45</v>
@@ -1317,7 +1374,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1333,19 +1390,19 @@
         <v>36</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>9</v>
@@ -1362,13 +1419,13 @@
         <v>43</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>9</v>
@@ -1391,13 +1448,13 @@
         <v>46</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>9</v>
@@ -1415,8 +1472,98 @@
         <v>21</v>
       </c>
     </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="M1:O1"/>
@@ -1424,13 +1571,14 @@
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H3:H6 H9:H12 F18:F19 H30:H31" type="list">
+  <dataValidations count="12">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H3:H6 H9:H12 F18:F19 H30:H31 G36:G37" type="list">
       <formula1>"Site visits,Award functions,Others"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:I6 I9:I12 H18:H19 H24:H25 I30:I31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:I6 I9:I12 H18:H19 H24:H25 I30:I31 H36:H37" type="list">
       <formula1>"Tamil Nadu,Karnataka"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1462,8 +1610,16 @@
       <formula1>"Select,SingleEntry,MultipleEntry"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E30:E31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E30:E31 F36:F37" type="list">
       <formula1>"1,2,3,4,5,6,7,8,9,"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C36:C37" type="list">
+      <formula1>"INS1,Silver,Platinum,Gold,Silver,Platinum,Gold	"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D36:E37" type="none">
+      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1482,58 +1638,65 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>74</v>
+        <v>81</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>91</v>
@@ -1542,7 +1705,7 @@
         <v>7708434845</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>12345</v>
@@ -1551,21 +1714,27 @@
         <v>1111</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>7708431267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>91</v>
@@ -1574,7 +1743,7 @@
         <v>7708434846</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>12345</v>
@@ -1583,21 +1752,27 @@
         <v>2222</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>7708431268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>91</v>
@@ -1606,7 +1781,7 @@
         <v>7708434847</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>12345</v>
@@ -1615,21 +1790,27 @@
         <v>3333</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>88</v>
+        <v>100</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>7708431269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>91</v>
@@ -1638,7 +1819,7 @@
         <v>7708434848</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>12345</v>
@@ -1647,21 +1828,27 @@
         <v>4444</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>7708431270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>91</v>
@@ -1670,7 +1857,7 @@
         <v>7708434849</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>12345</v>
@@ -1679,21 +1866,27 @@
         <v>5555</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>96</v>
+        <v>110</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>7708431271</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>91</v>
@@ -1702,7 +1895,7 @@
         <v>7708434850</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>12345</v>
@@ -1711,21 +1904,27 @@
         <v>6666</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>7708431272</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>91</v>
@@ -1734,7 +1933,7 @@
         <v>7708434851</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>12345</v>
@@ -1743,21 +1942,27 @@
         <v>7777</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>104</v>
+        <v>120</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>7708431273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>91</v>
@@ -1766,7 +1971,7 @@
         <v>7708434852</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>12345</v>
@@ -1775,21 +1980,27 @@
         <v>8888</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>108</v>
+        <v>125</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>7708431274</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>91</v>
@@ -1798,7 +2009,7 @@
         <v>7708434853</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>12345</v>
@@ -1807,7 +2018,13 @@
         <v>9999</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>111</v>
+        <v>129</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>7708431275</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1815,7 +2032,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -1827,262 +2044,262 @@
     </row>
     <row r="15" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>987654321</v>
+        <v>987644321</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>987654322</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>987654323</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>987654324</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>987654325</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>987654326</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>987654327</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>987654328</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>987654329</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2135,6 +2352,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="selvacorporate8@yopmail.com"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/src/test/resources/Credentialss.xlsx
+++ b/src/test/resources/Credentialss.xlsx
@@ -10,6 +10,8 @@
   <sheets>
     <sheet name="Flightbookingdetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="PassengerInformation" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="ManageScreen" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="CorporateCreation" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="216">
   <si>
     <t xml:space="preserve">Flight booking – Corporate Admin</t>
   </si>
@@ -164,12 +166,15 @@
     <t xml:space="preserve">Booked by Corporate User</t>
   </si>
   <si>
-    <t xml:space="preserve">Duba</t>
+    <t xml:space="preserve">Dubai</t>
   </si>
   <si>
     <t xml:space="preserve">Car booking</t>
   </si>
   <si>
+    <t xml:space="preserve">Voucher Fulfillment</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Location</t>
   </si>
   <si>
@@ -182,6 +187,33 @@
     <t xml:space="preserve">Pickup location</t>
   </si>
   <si>
+    <t xml:space="preserve">Car type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car Reg No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chauffeur Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chauffeur Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voucher Code</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nothing</t>
   </si>
   <si>
@@ -191,9 +223,27 @@
     <t xml:space="preserve">Official Meeting</t>
   </si>
   <si>
+    <t xml:space="preserve">Sedan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wagon R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCDE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Visa booking</t>
   </si>
   <si>
+    <t xml:space="preserve">Visa Fulfillment</t>
+  </si>
+  <si>
     <t xml:space="preserve">Country</t>
   </si>
   <si>
@@ -209,6 +259,36 @@
     <t xml:space="preserve">Onward date</t>
   </si>
   <si>
+    <t xml:space="preserve">Visa Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visa transaction type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online application charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Courier Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handling Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attestation charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board Charge</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indi</t>
   </si>
   <si>
@@ -218,9 +298,15 @@
     <t xml:space="preserve">MultipleEntry</t>
   </si>
   <si>
+    <t xml:space="preserve">OutStation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Insurance booking</t>
   </si>
   <si>
+    <t xml:space="preserve">Insurance Fulfillment</t>
+  </si>
+  <si>
     <t xml:space="preserve">Location</t>
   </si>
   <si>
@@ -236,6 +322,9 @@
     <t xml:space="preserve">No of Pax</t>
   </si>
   <si>
+    <t xml:space="preserve">Insurance Charge</t>
+  </si>
+  <si>
     <t xml:space="preserve">India</t>
   </si>
   <si>
@@ -275,30 +364,30 @@
     <t xml:space="preserve">Contact number</t>
   </si>
   <si>
+    <t xml:space="preserve">Guest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sundara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pandiyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selvacorporate8@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation-user one-1111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Employee</t>
   </si>
   <si>
-    <t xml:space="preserve">Mr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sundara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pandiyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selvacorporate8@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation-user one-1111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guest</t>
-  </si>
-  <si>
     <t xml:space="preserve">Karhi</t>
   </si>
   <si>
@@ -444,6 +533,144 @@
   </si>
   <si>
     <t xml:space="preserve">Male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manage Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Admin creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate User creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corpuser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autouser@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non User creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nonuser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nonuser@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No of employees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razor Pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCAvenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoops@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juhiii corporateee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madurai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.s1233.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juhi</t>
   </si>
 </sst>
 </file>
@@ -504,7 +731,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -526,13 +753,37 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFB4C7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FAF46"/>
+        <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB7B3CA"/>
-        <bgColor rgb="FFCC99FF"/>
+        <bgColor rgb="FFB4C7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF819E"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FFB7B3CA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -577,7 +828,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -602,11 +853,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -619,6 +878,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -656,7 +943,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -667,7 +954,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -680,9 +967,9 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF6B5E9B"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFBF819E"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF3FAF46"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -699,8 +986,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
-  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S37"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.48"/>
@@ -787,7 +1074,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -799,7 +1086,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>19</v>
@@ -830,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
@@ -877,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>16</v>
@@ -1244,7 +1531,7 @@
         <v>41</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>20</v>
@@ -1293,22 +1580,33 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
+      <c r="I22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>10</v>
@@ -1318,6 +1616,33 @@
       </c>
       <c r="H23" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1328,22 +1653,49 @@
         <v>44</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>45</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>123456</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>234678</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1354,16 +1706,16 @@
         <v>44</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>45</v>
@@ -1371,10 +1723,37 @@
       <c r="H25" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="I25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1384,25 +1763,37 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>9</v>
@@ -1412,6 +1803,36 @@
       </c>
       <c r="I29" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1419,13 +1840,13 @@
         <v>43</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>9</v>
@@ -1441,6 +1862,36 @@
       </c>
       <c r="I30" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1448,13 +1899,13 @@
         <v>46</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>9</v>
@@ -1471,10 +1922,40 @@
       <c r="I31" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="J31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S31" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1483,31 +1964,45 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
+      <c r="I34" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1515,10 +2010,10 @@
         <v>43</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>50</v>
@@ -1534,6 +2029,15 @@
       </c>
       <c r="H36" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1541,10 +2045,10 @@
         <v>46</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>55</v>
@@ -1561,17 +2065,29 @@
       <c r="H37" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="I37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A7:O7"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="I22:Q22"/>
     <mergeCell ref="A28:I28"/>
+    <mergeCell ref="J28:S28"/>
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="I34:K34"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H3:H6 H9:H12 F18:F19 H30:H31 G36:G37" type="list">
@@ -1639,7 +2155,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.6"/>
@@ -1649,54 +2165,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>91</v>
@@ -1704,8 +2220,8 @@
       <c r="F2" s="4" t="n">
         <v>7708434845</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>88</v>
+      <c r="G2" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>12345</v>
@@ -1714,10 +2230,10 @@
         <v>1111</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>7708431267</v>
@@ -1725,16 +2241,16 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>91</v>
@@ -1742,8 +2258,8 @@
       <c r="F3" s="4" t="n">
         <v>7708434846</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>94</v>
+      <c r="G3" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>12345</v>
@@ -1752,10 +2268,10 @@
         <v>2222</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>7708431268</v>
@@ -1763,16 +2279,16 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>91</v>
@@ -1780,8 +2296,8 @@
       <c r="F4" s="4" t="n">
         <v>7708434847</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>99</v>
+      <c r="G4" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>12345</v>
@@ -1790,10 +2306,10 @@
         <v>3333</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>7708431269</v>
@@ -1801,16 +2317,16 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>91</v>
@@ -1818,8 +2334,8 @@
       <c r="F5" s="4" t="n">
         <v>7708434848</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>104</v>
+      <c r="G5" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>12345</v>
@@ -1828,10 +2344,10 @@
         <v>4444</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>7708431270</v>
@@ -1839,16 +2355,16 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>91</v>
@@ -1856,8 +2372,8 @@
       <c r="F6" s="4" t="n">
         <v>7708434849</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>109</v>
+      <c r="G6" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>12345</v>
@@ -1866,10 +2382,10 @@
         <v>5555</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>7708431271</v>
@@ -1877,16 +2393,16 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>91</v>
@@ -1894,8 +2410,8 @@
       <c r="F7" s="4" t="n">
         <v>7708434850</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>114</v>
+      <c r="G7" s="10" t="s">
+        <v>143</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>12345</v>
@@ -1904,10 +2420,10 @@
         <v>6666</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>7708431272</v>
@@ -1915,16 +2431,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>91</v>
@@ -1932,8 +2448,8 @@
       <c r="F8" s="4" t="n">
         <v>7708434851</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>119</v>
+      <c r="G8" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>12345</v>
@@ -1942,10 +2458,10 @@
         <v>7777</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>7708431273</v>
@@ -1953,16 +2469,16 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>91</v>
@@ -1970,8 +2486,8 @@
       <c r="F9" s="4" t="n">
         <v>7708434852</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>124</v>
+      <c r="G9" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>12345</v>
@@ -1980,10 +2496,10 @@
         <v>8888</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>7708431274</v>
@@ -1991,16 +2507,16 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>91</v>
@@ -2008,8 +2524,8 @@
       <c r="F10" s="4" t="n">
         <v>7708434853</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>128</v>
+      <c r="G10" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>12345</v>
@@ -2018,288 +2534,288 @@
         <v>9999</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>7708431275</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G11" s="9"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="A14" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>137</v>
+      <c r="A15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>987644321</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>987654322</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>987654323</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>987654324</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>987654325</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>987654326</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>987654327</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>987654328</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>987654329</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>625402</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2363,4 +2879,486 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>7708464542</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>7708464545</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1321</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>7708464549</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:J8"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" display="auto@yopmail.com"/>
+    <hyperlink ref="D7" r:id="rId2" display="autouser@yopmail.com"/>
+    <hyperlink ref="D10" r:id="rId3" display="nonuser@yopmail.com"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:W3"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.42"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="4"/>
+    </row>
+    <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>7708434852</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>625402</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>7708434841</v>
+      </c>
+      <c r="P3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="W3" s="19" t="s">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" display="hoops@yopmail.com"/>
+    <hyperlink ref="N3" r:id="rId2" display="www.s1233.com"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/test/resources/Credentialss.xlsx
+++ b/src/test/resources/Credentialss.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Flightbookingdetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -1074,7 +1074,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>114</v>

--- a/src/test/resources/Credentialss.xlsx
+++ b/src/test/resources/Credentialss.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="217">
   <si>
     <t xml:space="preserve">Flight booking – Corporate Admin</t>
   </si>
@@ -91,45 +91,48 @@
     <t xml:space="preserve">Tamil Nadu</t>
   </si>
   <si>
+    <t xml:space="preserve">AI Express</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refundable Fare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic – RT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hahn Air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International – OW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singapore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuwait Airways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International – RT</t>
+  </si>
+  <si>
     <t xml:space="preserve">No Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Flight booking – Corporate User</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 stop</t>
   </si>
   <si>
-    <t xml:space="preserve">Refundable Fare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domestic – RT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hahn Air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International – OW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DXB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singapore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Stop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International – RT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuwait Airways</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flight booking – Corporate User</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hotel booking</t>
   </si>
   <si>
@@ -364,7 +367,7 @@
     <t xml:space="preserve">Contact number</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest</t>
+    <t xml:space="preserve">Employee</t>
   </si>
   <si>
     <t xml:space="preserve">Mr</t>
@@ -385,9 +388,6 @@
     <t xml:space="preserve">Ajay</t>
   </si>
   <si>
-    <t xml:space="preserve">Employee</t>
-  </si>
-  <si>
     <t xml:space="preserve">Karhi</t>
   </si>
   <si>
@@ -553,21 +553,24 @@
     <t xml:space="preserve">Employee number</t>
   </si>
   <si>
+    <t xml:space="preserve">Harishh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kumarr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hari12@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate User creation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">auto@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corporate Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corporate User creation</t>
-  </si>
-  <si>
     <t xml:space="preserve">corpuser</t>
   </si>
   <si>
@@ -637,7 +640,7 @@
     <t xml:space="preserve">Bill name</t>
   </si>
   <si>
-    <t xml:space="preserve">Automati</t>
+    <t xml:space="preserve">Hariiii</t>
   </si>
   <si>
     <t xml:space="preserve">User</t>
@@ -649,10 +652,10 @@
     <t xml:space="preserve">Mech</t>
   </si>
   <si>
-    <t xml:space="preserve">hoops@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juhiii corporateee</t>
+    <t xml:space="preserve">Hariiii12@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harii corporatee</t>
   </si>
   <si>
     <t xml:space="preserve">Madurai</t>
@@ -670,7 +673,7 @@
     <t xml:space="preserve">Y</t>
   </si>
   <si>
-    <t xml:space="preserve">Juhi</t>
+    <t xml:space="preserve">Hariii</t>
   </si>
 </sst>
 </file>
@@ -987,7 +990,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S37"/>
-  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.48"/>
@@ -1086,7 +1089,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>19</v>
@@ -1188,10 +1191,10 @@
         <v>21</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>24</v>
@@ -1232,7 +1235,7 @@
         <v>33</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>24</v>
@@ -1336,10 +1339,10 @@
         <v>21</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>24</v>
@@ -1379,10 +1382,10 @@
         <v>21</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>24</v>
@@ -1391,7 +1394,7 @@
         <v>27</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>24</v>
@@ -1426,10 +1429,10 @@
         <v>21</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>24</v>
@@ -1467,10 +1470,10 @@
         <v>21</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>24</v>
@@ -1481,7 +1484,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1493,36 +1496,36 @@
     </row>
     <row r="17" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>27</v>
@@ -1537,7 +1540,7 @@
         <v>20</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>21</v>
@@ -1545,10 +1548,10 @@
     </row>
     <row r="19" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>51</v>
@@ -1563,7 +1566,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>21</v>
@@ -1571,7 +1574,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1581,7 +1584,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
@@ -1594,90 +1597,90 @@
     </row>
     <row r="23" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>40</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>123456</v>
@@ -1686,7 +1689,7 @@
         <v>234678</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O24" s="4" t="n">
         <v>1000</v>
@@ -1695,30 +1698,30 @@
         <v>123</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>45</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>21</v>
@@ -1753,7 +1756,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1764,7 +1767,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
@@ -1778,22 +1781,22 @@
     </row>
     <row r="29" customFormat="false" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>9</v>
@@ -1802,51 +1805,51 @@
         <v>10</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>9</v>
@@ -1867,7 +1870,7 @@
         <v>100</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>100</v>
@@ -1896,16 +1899,16 @@
     </row>
     <row r="31" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>9</v>
@@ -1955,7 +1958,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1965,55 +1968,55 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>50</v>
@@ -2042,13 +2045,13 @@
     </row>
     <row r="37" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>55</v>
@@ -2155,7 +2158,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.6"/>
@@ -2165,54 +2168,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>91</v>
@@ -2221,7 +2224,7 @@
         <v>7708434845</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>12345</v>
@@ -2230,10 +2233,10 @@
         <v>1111</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>7708431267</v>
@@ -2241,10 +2244,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>121</v>
@@ -2279,10 +2282,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>126</v>
@@ -2317,10 +2320,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>131</v>
@@ -2355,10 +2358,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>136</v>
@@ -2393,10 +2396,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>141</v>
@@ -2431,10 +2434,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>146</v>
@@ -2469,10 +2472,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>151</v>
@@ -2507,10 +2510,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>156</v>
@@ -2560,10 +2563,10 @@
     </row>
     <row r="15" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>161</v>
@@ -2586,10 +2589,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>987644321</v>
@@ -2887,7 +2890,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.63"/>
   </cols>
@@ -2922,7 +2925,7 @@
     </row>
     <row r="3" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>172</v>
@@ -2931,30 +2934,30 @@
         <v>173</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>174</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>175</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>176</v>
@@ -2969,13 +2972,13 @@
         <v>91</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7708464542</v>
+        <v>7708064542</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1234</v>
+        <v>1298</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>21</v>
@@ -3000,7 +3003,7 @@
     </row>
     <row r="6" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>172</v>
@@ -3009,39 +3012,39 @@
         <v>173</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>174</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>175</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>91</v>
@@ -3053,18 +3056,18 @@
         <v>1321</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -3078,7 +3081,7 @@
     </row>
     <row r="9" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>172</v>
@@ -3087,39 +3090,39 @@
         <v>173</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>174</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>175</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>91</v>
@@ -3131,13 +3134,13 @@
         <v>1322</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -3148,7 +3151,7 @@
     <mergeCell ref="A8:J8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="auto@yopmail.com"/>
+    <hyperlink ref="D4" r:id="rId1" display="Hari12@yopmail.com"/>
     <hyperlink ref="D7" r:id="rId2" display="autouser@yopmail.com"/>
     <hyperlink ref="D10" r:id="rId3" display="nonuser@yopmail.com"/>
   </hyperlinks>
@@ -3168,14 +3171,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W3"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -3194,7 +3197,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
       <c r="R1" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="S1" s="12"/>
       <c r="T1" s="12"/>
@@ -3204,117 +3207,117 @@
     </row>
     <row r="2" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>164</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>165</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F3" s="15" t="n">
         <v>7708434852</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M3" s="15" t="n">
         <v>625402</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O3" s="15" t="n">
         <v>7708434841</v>
@@ -3323,25 +3326,25 @@
         <v>2</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="W3" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +3353,7 @@
     <mergeCell ref="R1:V1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" display="hoops@yopmail.com"/>
+    <hyperlink ref="G3" r:id="rId1" display="Hariiii12@yopmail.com"/>
     <hyperlink ref="N3" r:id="rId2" display="www.s1233.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
